--- a/danh-gia-pha-b/sa22-giao-nguoi-cham/thu-sa22-C2.xlsx
+++ b/danh-gia-pha-b/sa22-giao-nguoi-cham/thu-sa22-C2.xlsx
@@ -835,10 +835,26 @@
       <c r="A33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Đọc hướng dẫn SA-22 và chấm thử 20 câu</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1149,15 +1165,45 @@
           <t>xstk-ch3-1</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
+      <c r="J2" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L2" s="10" t="n"/>
     </row>
     <row r="3">
@@ -1171,16 +1217,54 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Phương án nhiễu A dùng từ tuyệt đối "hoàn toàn"</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -1193,15 +1277,45 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I4" s="10" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
+      <c r="J4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L4" s="10" t="n"/>
     </row>
     <row r="5">
@@ -1215,16 +1329,54 @@
           <t>doc-1</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="10" t="n"/>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="n"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>L10,L12,L13</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>bo</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Câu trích bị cắt cụt vế đầu ("lần lượt là...") và lặp từ "chính tắc"</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -1237,16 +1389,54 @@
           <t>xstk-ch3-1</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>L01,L10,L13</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>bo</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>khong_chac; Câu trích từ đề bài ví dụ, thiếu ngữ cảnh nên cả A (Giả thiết thống kê) và B (Giả thiết H) đều hợp lý</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1259,15 +1449,45 @@
           <t>nhap-mon-ml</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>hieu</t>
+        </is>
+      </c>
       <c r="I7" s="10" t="n"/>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="10" t="n"/>
+      <c r="J7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L7" s="10" t="n"/>
     </row>
     <row r="8">
@@ -1281,15 +1501,49 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="10" t="n"/>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L8" s="10" t="n"/>
     </row>
     <row r="9">
@@ -1303,16 +1557,54 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="10" t="n"/>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>L10,L15</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>sua_nhe</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Lỗi khoảng trắng OCR "bảo t ồ n n ội dung" trong câu dẫn</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1325,15 +1617,45 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
+      <c r="J10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L10" s="10" t="n"/>
     </row>
     <row r="11">
@@ -1347,16 +1669,50 @@
           <t>xstk-ch3-1</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I11" s="10" t="n"/>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="10" t="n"/>
+      <c r="J11" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>Câu hỏi kiểm tra khái niệm Độ tin cậy (1-α), không phải Khoảng ước lượng</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1369,16 +1725,54 @@
           <t>doc-1</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>L02,L10,L15</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>sua_nhe</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>Phương án nhiễu B là tên định lý không khớp ngữ pháp; cuối câu thiếu cụm "của W"</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1391,15 +1785,45 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
+      <c r="J13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L13" s="10" t="n"/>
     </row>
     <row r="14">
@@ -1413,15 +1837,45 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
+      <c r="J14" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L14" s="10" t="n"/>
     </row>
     <row r="15">
@@ -1435,15 +1889,45 @@
           <t>xstk-ch3-1</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I15" s="10" t="n"/>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="10" t="n"/>
+      <c r="J15" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L15" s="10" t="n"/>
     </row>
     <row r="16">
@@ -1457,15 +1941,45 @@
           <t>nhap-mon-ml</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>hieu</t>
+        </is>
+      </c>
       <c r="I16" s="10" t="n"/>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="10" t="n"/>
+      <c r="J16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L16" s="10" t="n"/>
     </row>
     <row r="17">
@@ -1479,15 +1993,45 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>hieu</t>
+        </is>
+      </c>
       <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
+      <c r="J17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L17" s="10" t="n"/>
     </row>
     <row r="18">
@@ -1501,16 +2045,54 @@
           <t>nhap-mon-ml</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>L10,L13</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>sua_nhe</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>Câu trích bắt đầu bằng "Nói cách khác" thiếu ngữ cảnh phía trước</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -1523,16 +2105,54 @@
           <t>nhap-mon-ml</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>L10,L13</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>sua_nhe</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>Câu trích bắt đầu bằng "Nói cách khác" thiếu ngữ cảnh phía trước</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1545,16 +2165,54 @@
           <t>xstk-ch3-1</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>L10,L13</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>bo</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>Đục lỗ trên dòng tiêu đề mục con, không phải câu định nghĩa hoàn chỉnh</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -1567,15 +2225,45 @@
           <t>doc-4</t>
         </is>
       </c>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>nho</t>
+        </is>
+      </c>
       <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
+      <c r="J21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>dung_ngay</t>
+        </is>
+      </c>
       <c r="L21" s="10" t="n"/>
     </row>
   </sheetData>
@@ -1639,19 +2327,31 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="n"/>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Các câu điền khuyết (L10) chiếm tỷ lệ đáng kể; một số câu bị cắt cụt vế đầu ("lần lượt là...", "Nói cách khác...") hoặc đục lỗ ngay trên tiêu đề mục ("• Ước lượng khoảng - Phương pháp ___" ở T18).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="n"/>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Câu T03 đục lỗ trên câu hỏi đề bài ví dụ ("Hãy sử dụng mẫu trên để kiểm định ___") khiến cả A (Giả thiết thống kê) và B (Giả thiết H) đều hợp lý khi thiếu ngữ cảnh.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="n"/>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Câu T10 hỏi tên gọi của giá trị 1-α (Độ tin cậy) nhưng mục "Khái niệm câu này kiểm" trong khối đáp án lại ghi là "Khoảng ước lượng".</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
